--- a/XLibur.Tests/Resource/Other/InlineStrings/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/InlineStrings/outputfile.xlsx
@@ -529,506 +529,499 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A2:B63"/>
   <x:sheetFormatPr defaultRowHeight="14.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:2" hidden="1"/>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2494</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="A5" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>10041</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="A6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>61631</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="A7" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="A8" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>40120</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
-      <x:c r="A9" s="0" t="s">
+      <x:c r="A9" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
-      <x:c r="A10" s="0" t="s">
+      <x:c r="A10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="0">
+      <x:c r="B10">
         <x:v>96621</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
-      <x:c r="A11" s="0" t="s">
+      <x:c r="A11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="0">
+      <x:c r="B11">
         <x:v>613844</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
-      <x:c r="A12" s="0" t="s">
+      <x:c r="A12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>79917</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
-      <x:c r="A13" s="0" t="s">
+      <x:c r="A13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="0">
+      <x:c r="B13">
         <x:v>59172</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
-      <x:c r="A14" s="0" t="s">
+      <x:c r="A14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="0">
+      <x:c r="B14">
         <x:v>8464</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
-      <x:c r="A15" s="0" t="s">
+      <x:c r="A15" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="0">
+      <x:c r="B15">
         <x:v>13917</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
-      <x:c r="A16" s="0" t="s">
+      <x:c r="A16" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="0">
+      <x:c r="B16">
         <x:v>366105</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
-      <x:c r="A17" s="0" t="s">
+      <x:c r="A17" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="0">
+      <x:c r="B17">
         <x:v>130540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
-      <x:c r="A18" s="0" t="s">
+      <x:c r="A18" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="0">
+      <x:c r="B18">
         <x:v>2465</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
-      <x:c r="A19" s="0" t="s">
+      <x:c r="A19" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B19" s="0">
+      <x:c r="B19">
         <x:v>21737</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
-      <x:c r="A20" s="0" t="s">
+      <x:c r="A20" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="0">
+      <x:c r="B20">
         <x:v>47578</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
-      <x:c r="A21" s="0" t="s">
+      <x:c r="A21" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B21" s="0">
+      <x:c r="B21">
         <x:v>25007</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
-      <x:c r="A22" s="0" t="s">
+      <x:c r="A22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B22" s="0">
+      <x:c r="B22">
         <x:v>186534</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
-      <x:c r="A23" s="0" t="s">
+      <x:c r="A23" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B23" s="0">
+      <x:c r="B23">
         <x:v>88108</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
-      <x:c r="A24" s="0" t="s">
+      <x:c r="A24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B24" s="0">
+      <x:c r="B24">
         <x:v>41361</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
-      <x:c r="A25" s="0" t="s">
+      <x:c r="A25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B25" s="0">
+      <x:c r="B25">
         <x:v>59488</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
-      <x:c r="A26" s="0" t="s">
+      <x:c r="A26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B26" s="0">
+      <x:c r="B26">
         <x:v>59583</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
-      <x:c r="A27" s="0" t="s">
+      <x:c r="A27" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B27" s="0">
+      <x:c r="B27">
         <x:v>120485</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
-      <x:c r="A28" s="0" t="s">
+      <x:c r="A28" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B28" s="0">
+      <x:c r="B28">
         <x:v>92578</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
-      <x:c r="A29" s="0" t="s">
+      <x:c r="A29" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B29" s="0">
+      <x:c r="B29">
         <x:v>19889</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
-      <x:c r="A30" s="0" t="s">
+      <x:c r="A30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B30" s="0">
+      <x:c r="B30">
         <x:v>149924</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
-      <x:c r="A31" s="0" t="s">
+      <x:c r="A31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B31" s="0">
+      <x:c r="B31">
         <x:v>94877</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
-      <x:c r="A32" s="0" t="s">
+      <x:c r="A32" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B32" s="0">
+      <x:c r="B32">
         <x:v>83686</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
-      <x:c r="A33" s="0" t="s">
+      <x:c r="A33" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B33" s="0">
+      <x:c r="B33">
         <x:v>406</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
-      <x:c r="A34" s="0" t="s">
+      <x:c r="A34" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B34" s="0">
+      <x:c r="B34">
         <x:v>35746</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
-      <x:c r="A35" s="0" t="s">
+      <x:c r="A35" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B35" s="0">
+      <x:c r="B35">
         <x:v>15699</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
-      <x:c r="A36" s="0" t="s">
+      <x:c r="A36" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B36" s="0">
+      <x:c r="B36">
         <x:v>142274</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
-      <x:c r="A37" s="0" t="s">
+      <x:c r="A37" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B37" s="0">
+      <x:c r="B37">
         <x:v>12755</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
-      <x:c r="A38" s="0" t="s">
+      <x:c r="A38" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B38" s="0">
+      <x:c r="B38">
         <x:v>29806</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
-      <x:c r="A39" s="0" t="s">
+      <x:c r="A39" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B39" s="0">
+      <x:c r="B39">
         <x:v>22771</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
-      <x:c r="A40" s="0" t="s">
+      <x:c r="A40" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B40" s="0">
+      <x:c r="B40">
         <x:v>157926</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
-      <x:c r="A41" s="0" t="s">
+      <x:c r="A41" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B41" s="0">
+      <x:c r="B41">
         <x:v>25904</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
-      <x:c r="A42" s="0" t="s">
+      <x:c r="A42" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B42" s="0">
+      <x:c r="B42">
         <x:v>44534</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
-      <x:c r="A43" s="0" t="s">
+      <x:c r="A43" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B43" s="0">
+      <x:c r="B43">
         <x:v>342298</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
-      <x:c r="A44" s="0" t="s">
+      <x:c r="A44" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B44" s="0">
+      <x:c r="B44">
         <x:v>185713</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
-      <x:c r="A45" s="0" t="s">
+      <x:c r="A45" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B45" s="0">
+      <x:c r="B45">
         <x:v>48861</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:2">
-      <x:c r="A46" s="0" t="s">
+      <x:c r="A46" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B46" s="0">
+      <x:c r="B46">
         <x:v>65474</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:2">
-      <x:c r="A47" s="0" t="s">
+      <x:c r="A47" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B47" s="0">
+      <x:c r="B47">
         <x:v>203386</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
-      <x:c r="A48" s="0" t="s">
+      <x:c r="A48" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B48" s="0">
+      <x:c r="B48">
         <x:v>52344</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
-      <x:c r="A49" s="0" t="s">
+      <x:c r="A49" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B49" s="0">
+      <x:c r="B49">
         <x:v>19816</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
-      <x:c r="A50" s="0" t="s">
+      <x:c r="A50" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B50" s="0">
+      <x:c r="B50">
         <x:v>65340</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
-      <x:c r="A51" s="0" t="s">
+      <x:c r="A51" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B51" s="0">
+      <x:c r="B51">
         <x:v>13427</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
-      <x:c r="A52" s="0" t="s">
+      <x:c r="A52" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B52" s="0">
+      <x:c r="B52">
         <x:v>91541</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
-      <x:c r="A53" s="0" t="s">
+      <x:c r="A53" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B53" s="0">
+      <x:c r="B53">
         <x:v>394702</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
-      <x:c r="A54" s="0" t="s">
+      <x:c r="A54" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B54" s="0">
+      <x:c r="B54">
         <x:v>42780</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
-      <x:c r="A55" s="0" t="s">
+      <x:c r="A55" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B55" s="0">
+      <x:c r="B55">
         <x:v>126069</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
-      <x:c r="A56" s="0" t="s">
+      <x:c r="A56" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B56" s="0">
+      <x:c r="B56">
         <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
-      <x:c r="A57" s="0" t="s">
+      <x:c r="A57" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B57" s="0">
+      <x:c r="B57">
         <x:v>10051</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
-      <x:c r="A58" s="0" t="s">
+      <x:c r="A58" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B58" s="0">
+      <x:c r="B58">
         <x:v>115953</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
-      <x:c r="A59" s="0" t="s">
+      <x:c r="A59" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B59" s="0">
+      <x:c r="B59">
         <x:v>85362</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
-      <x:c r="A60" s="0" t="s">
+      <x:c r="A60" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B60" s="0">
+      <x:c r="B60">
         <x:v>25646</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
-      <x:c r="A61" s="0" t="s">
+      <x:c r="A61" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B61" s="0">
+      <x:c r="B61">
         <x:v>8352</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
-      <x:c r="A63" s="0" t="s">
+      <x:c r="A63" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B63" s="0">
+      <x:c r="B63">
         <x:v>4962691</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>